--- a/QBAF_relevanceScoreHumanLabeled.xlsx
+++ b/QBAF_relevanceScoreHumanLabeled.xlsx
@@ -8,19 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wu-my.sharepoint.com/personal/h12328919_s_wu_ac_at/Documents/Dokumente/Uni/Claude/BA/BA_Code/temp2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{52DC61B2-9161-1B44-B4CB-53D58410C4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A7BF998-9CC0-7D4A-8521-BEA1E22A69CD}"/>
+  <xr:revisionPtr revIDLastSave="216" documentId="8_{52DC61B2-9161-1B44-B4CB-53D58410C4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C5BF585-6366-6143-B355-E8A4EFCFC581}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" xr2:uid="{B9BBEF74-3CC3-0F4D-96E7-5EED1D1E623F}"/>
   </bookViews>
   <sheets>
     <sheet name="QBAF_relevanceScoreHumanLabeled" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="208">
   <si>
     <t>arg1</t>
   </si>
@@ -46,6 +62,9 @@
     <t>#2_relevance: human labeled</t>
   </si>
   <si>
+    <t>support human labeled</t>
+  </si>
+  <si>
     <t>The voting age should be lowered to sixteen years</t>
   </si>
   <si>
@@ -58,6 +77,9 @@
     <t>idebate</t>
   </si>
   <si>
+    <t>0.25</t>
+  </si>
+  <si>
     <t>an appeal to one narrow religious text isnt very persuasive</t>
   </si>
   <si>
@@ -79,6 +101,9 @@
     <t>web</t>
   </si>
   <si>
+    <t>0.5</t>
+  </si>
+  <si>
     <t>actually im not sure its been proven</t>
   </si>
   <si>
@@ -229,6 +254,9 @@
     <t>Politicians should be able to make difficult decisions without fear that selecting one option will lead to their incarceration</t>
   </si>
   <si>
+    <t>0.75</t>
+  </si>
+  <si>
     <t>People are not voting for UKIP because of immigration propaganda but because of their direct experience of immigration.</t>
   </si>
   <si>
@@ -632,9 +660,6 @@
   </si>
   <si>
     <t>The charge put by its deputy leader David Campbell Bannerman when he defected to the Conservatives in the wake of the May elections was that UKIP remained, at heart, a single issue pressure group.</t>
-  </si>
-  <si>
-    <t>support human labeled</t>
   </si>
 </sst>
 </file>
@@ -1178,10 +1203,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1500,20 +1521,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D224C079-FBF6-2442-8650-62051FAE21A1}">
   <dimension ref="A1:K101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="76.6640625" customWidth="1"/>
-    <col min="2" max="2" width="100.33203125" customWidth="1"/>
-    <col min="3" max="3" width="7.33203125" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1640625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="22.1640625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="78.33203125" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" customWidth="1"/>
+    <col min="1" max="1" width="66.83203125" customWidth="1"/>
+    <col min="2" max="2" width="86.33203125" customWidth="1"/>
+    <col min="3" max="5" width="1.1640625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="1.33203125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="1.6640625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="9" max="10" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1539,30 +1558,24 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>204</v>
-      </c>
-      <c r="J1">
-        <v>0</v>
-      </c>
-      <c r="K1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2">
         <v>3847</v>
@@ -1570,28 +1583,28 @@
       <c r="G2">
         <v>0.25</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3">
         <v>3123</v>
@@ -1599,28 +1612,28 @@
       <c r="G3">
         <v>0.25</v>
       </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>2214</v>
@@ -1628,22 +1641,28 @@
       <c r="G4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5">
         <v>3211</v>
@@ -1651,22 +1670,28 @@
       <c r="G5">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>2247</v>
@@ -1674,22 +1699,28 @@
       <c r="G6">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F7">
         <v>2580</v>
@@ -1697,22 +1728,28 @@
       <c r="G7">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F8">
         <v>2900</v>
@@ -1720,22 +1757,28 @@
       <c r="G8">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F9">
         <v>1646</v>
@@ -1743,22 +1786,28 @@
       <c r="G9">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F10">
         <v>3076</v>
@@ -1766,22 +1815,28 @@
       <c r="G10">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F11">
         <v>629</v>
@@ -1789,22 +1844,28 @@
       <c r="G11">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F12">
         <v>2912</v>
@@ -1812,22 +1873,28 @@
       <c r="G12">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F13">
         <v>238</v>
@@ -1835,22 +1902,28 @@
       <c r="G13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F14">
         <v>1847</v>
@@ -1858,22 +1931,28 @@
       <c r="G14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F15">
         <v>2272</v>
@@ -1881,22 +1960,28 @@
       <c r="G15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F16">
         <v>618</v>
@@ -1904,22 +1989,28 @@
       <c r="G16">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F17">
         <v>1020</v>
@@ -1927,22 +2018,28 @@
       <c r="G17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F18">
         <v>846</v>
@@ -1950,22 +2047,28 @@
       <c r="G18">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H18" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C19">
         <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F19">
         <v>816</v>
@@ -1973,22 +2076,28 @@
       <c r="G19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F20">
         <v>3128</v>
@@ -1996,22 +2105,28 @@
       <c r="G20">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H20" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F21">
         <v>3702</v>
@@ -2019,22 +2134,28 @@
       <c r="G21">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F22">
         <v>2727</v>
@@ -2042,22 +2163,28 @@
       <c r="G22">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F23">
         <v>1559</v>
@@ -2065,22 +2192,28 @@
       <c r="G23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E24" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F24">
         <v>704</v>
@@ -2088,22 +2221,28 @@
       <c r="G24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C25">
         <v>2</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E25" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F25">
         <v>282</v>
@@ -2111,22 +2250,28 @@
       <c r="G25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E26" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F26">
         <v>3093</v>
@@ -2134,22 +2279,28 @@
       <c r="G26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C27">
         <v>2</v>
       </c>
       <c r="D27" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E27" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F27">
         <v>851</v>
@@ -2157,22 +2308,28 @@
       <c r="G27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E28" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F28">
         <v>3808</v>
@@ -2180,22 +2337,28 @@
       <c r="G28">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H28" t="s">
+        <v>72</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
       <c r="D29" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E29" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F29">
         <v>1412</v>
@@ -2203,22 +2366,28 @@
       <c r="G29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H29" t="s">
+        <v>13</v>
+      </c>
+      <c r="I29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C30">
         <v>2</v>
       </c>
       <c r="D30" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E30" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F30">
         <v>606</v>
@@ -2226,22 +2395,28 @@
       <c r="G30">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F31">
         <v>3867</v>
@@ -2249,22 +2424,28 @@
       <c r="G31">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H31" t="s">
+        <v>72</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E32" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -2272,22 +2453,28 @@
       <c r="G32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E33" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F33">
         <v>550</v>
@@ -2295,22 +2482,28 @@
       <c r="G33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C34">
         <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E34" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F34">
         <v>3583</v>
@@ -2318,22 +2511,28 @@
       <c r="G34">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H34" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B35" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E35" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F35">
         <v>3210</v>
@@ -2341,22 +2540,28 @@
       <c r="G35">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E36" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F36">
         <v>2637</v>
@@ -2364,22 +2569,28 @@
       <c r="G36">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H36" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C37">
         <v>1</v>
       </c>
       <c r="D37" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E37" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F37">
         <v>3426</v>
@@ -2387,22 +2598,28 @@
       <c r="G37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F38">
         <v>2849</v>
@@ -2410,22 +2627,28 @@
       <c r="G38">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C39">
         <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E39" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F39">
         <v>2145</v>
@@ -2433,22 +2656,28 @@
       <c r="G39">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H39" t="s">
+        <v>21</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C40">
         <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E40" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F40">
         <v>397</v>
@@ -2456,22 +2685,28 @@
       <c r="G40">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C41">
         <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E41" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F41">
         <v>1867</v>
@@ -2479,22 +2714,28 @@
       <c r="G41">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E42" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F42">
         <v>2767</v>
@@ -2502,22 +2743,28 @@
       <c r="G42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H42" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E43" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F43">
         <v>3544</v>
@@ -2525,22 +2772,28 @@
       <c r="G43">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C44">
         <v>1</v>
       </c>
       <c r="D44" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E44" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F44">
         <v>2598</v>
@@ -2548,22 +2801,28 @@
       <c r="G44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H44" t="s">
+        <v>13</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B45" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C45">
         <v>1</v>
       </c>
       <c r="D45" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E45" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F45">
         <v>2655</v>
@@ -2571,22 +2830,28 @@
       <c r="G45">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B46" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C46">
         <v>1</v>
       </c>
       <c r="D46" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E46" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F46">
         <v>1520</v>
@@ -2594,22 +2859,28 @@
       <c r="G46">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B47" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E47" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F47">
         <v>3876</v>
@@ -2617,22 +2888,28 @@
       <c r="G47">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H47" t="s">
+        <v>21</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B48" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C48">
         <v>0</v>
       </c>
       <c r="D48" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E48" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F48">
         <v>3316</v>
@@ -2640,22 +2917,34 @@
       <c r="G48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>2</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B49" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C49">
         <v>1</v>
       </c>
       <c r="D49" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E49" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F49">
         <v>3807</v>
@@ -2663,22 +2952,34 @@
       <c r="G49">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B50" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C50">
         <v>1</v>
       </c>
       <c r="D50" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E50" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F50">
         <v>1295</v>
@@ -2686,22 +2987,34 @@
       <c r="G50">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H50" t="s">
+        <v>13</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50">
+        <v>2</v>
+      </c>
+      <c r="K50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B51" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C51">
         <v>2</v>
       </c>
       <c r="D51" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E51" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F51">
         <v>81</v>
@@ -2709,22 +3022,28 @@
       <c r="G51">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B52" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C52">
         <v>1</v>
       </c>
       <c r="D52" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E52" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F52">
         <v>2425</v>
@@ -2732,22 +3051,28 @@
       <c r="G52">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B53" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C53">
         <v>2</v>
       </c>
       <c r="D53" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E53" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F53">
         <v>1269</v>
@@ -2755,22 +3080,28 @@
       <c r="G53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B54" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C54">
         <v>1</v>
       </c>
       <c r="D54" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E54" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F54">
         <v>3712</v>
@@ -2778,22 +3109,28 @@
       <c r="G54">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H54">
+        <v>1</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B55" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C55">
         <v>2</v>
       </c>
       <c r="D55" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E55" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F55">
         <v>2078</v>
@@ -2801,22 +3138,28 @@
       <c r="G55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B56" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C56">
         <v>1</v>
       </c>
       <c r="D56" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E56" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F56">
         <v>1676</v>
@@ -2824,22 +3167,28 @@
       <c r="G56">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B57" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C57">
         <v>2</v>
       </c>
       <c r="D57" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E57" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F57">
         <v>1357</v>
@@ -2847,22 +3196,28 @@
       <c r="G57">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B58" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
       <c r="D58" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E58" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F58">
         <v>2197</v>
@@ -2870,22 +3225,25 @@
       <c r="G58">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B59" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E59" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F59">
         <v>3495</v>
@@ -2893,22 +3251,25 @@
       <c r="G59">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B60" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E60" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F60">
         <v>3838</v>
@@ -2916,22 +3277,25 @@
       <c r="G60">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B61" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E61" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F61">
         <v>1663</v>
@@ -2939,22 +3303,25 @@
       <c r="G61">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B62" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C62">
         <v>2</v>
       </c>
       <c r="D62" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E62" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F62">
         <v>1084</v>
@@ -2962,22 +3329,25 @@
       <c r="G62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B63" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E63" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F63">
         <v>2187</v>
@@ -2985,22 +3355,25 @@
       <c r="G63">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
+        <v>139</v>
+      </c>
+      <c r="B64" t="s">
         <v>135</v>
       </c>
-      <c r="B64" t="s">
-        <v>131</v>
-      </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E64" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F64">
         <v>1697</v>
@@ -3008,22 +3381,25 @@
       <c r="G64">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B65" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E65" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F65">
         <v>2618</v>
@@ -3031,22 +3407,25 @@
       <c r="G65">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B66" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C66">
         <v>1</v>
       </c>
       <c r="D66" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E66" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F66">
         <v>3417</v>
@@ -3054,22 +3433,25 @@
       <c r="G66">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B67" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C67">
         <v>2</v>
       </c>
       <c r="D67" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E67" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F67">
         <v>1869</v>
@@ -3077,22 +3459,25 @@
       <c r="G67">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B68" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C68">
         <v>1</v>
       </c>
       <c r="D68" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E68" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F68">
         <v>3326</v>
@@ -3100,22 +3485,25 @@
       <c r="G68">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B69" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E69" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F69">
         <v>2308</v>
@@ -3123,22 +3511,25 @@
       <c r="G69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B70" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C70">
         <v>2</v>
       </c>
       <c r="D70" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E70" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F70">
         <v>1620</v>
@@ -3146,22 +3537,25 @@
       <c r="G70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B71" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E71" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F71">
         <v>3897</v>
@@ -3169,22 +3563,25 @@
       <c r="G71">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B72" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C72">
         <v>1</v>
       </c>
       <c r="D72" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E72" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F72">
         <v>2527</v>
@@ -3192,22 +3589,25 @@
       <c r="G72">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B73" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C73">
         <v>2</v>
       </c>
       <c r="D73" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E73" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F73">
         <v>403</v>
@@ -3215,22 +3615,25 @@
       <c r="G73">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B74" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E74" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F74">
         <v>2450</v>
@@ -3238,22 +3641,25 @@
       <c r="G74">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B75" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E75" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F75">
         <v>1612</v>
@@ -3261,22 +3667,25 @@
       <c r="G75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B76" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C76">
         <v>1</v>
       </c>
       <c r="D76" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E76" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F76">
         <v>1041</v>
@@ -3284,22 +3693,25 @@
       <c r="G76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B77" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E77" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F77">
         <v>296</v>
@@ -3307,22 +3719,25 @@
       <c r="G77">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B78" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E78" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F78">
         <v>2547</v>
@@ -3330,22 +3745,25 @@
       <c r="G78">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B79" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C79">
         <v>2</v>
       </c>
       <c r="D79" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E79" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F79">
         <v>1465</v>
@@ -3353,22 +3771,25 @@
       <c r="G79">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B80" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C80">
         <v>2</v>
       </c>
       <c r="D80" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E80" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F80">
         <v>987</v>
@@ -3376,22 +3797,25 @@
       <c r="G80">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B81" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C81">
         <v>2</v>
       </c>
       <c r="D81" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E81" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F81">
         <v>1142</v>
@@ -3399,22 +3823,25 @@
       <c r="G81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B82" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C82">
         <v>2</v>
       </c>
       <c r="D82" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E82" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F82">
         <v>143</v>
@@ -3422,22 +3849,25 @@
       <c r="G82">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B83" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C83">
         <v>1</v>
       </c>
       <c r="D83" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E83" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F83">
         <v>3045</v>
@@ -3445,22 +3875,25 @@
       <c r="G83">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H83" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B84" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C84">
         <v>1</v>
       </c>
       <c r="D84" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E84" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F84">
         <v>2609</v>
@@ -3468,22 +3901,25 @@
       <c r="G84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B85" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C85">
         <v>2</v>
       </c>
       <c r="D85" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E85" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F85">
         <v>1341</v>
@@ -3491,22 +3927,25 @@
       <c r="G85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B86" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C86">
         <v>1</v>
       </c>
       <c r="D86" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E86" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F86">
         <v>3198</v>
@@ -3514,22 +3953,25 @@
       <c r="G86">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B87" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C87">
         <v>1</v>
       </c>
       <c r="D87" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E87" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F87">
         <v>3182</v>
@@ -3537,22 +3979,25 @@
       <c r="G87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B88" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C88">
         <v>2</v>
       </c>
       <c r="D88" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E88" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F88">
         <v>1870</v>
@@ -3560,22 +4005,25 @@
       <c r="G88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B89" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C89">
         <v>1</v>
       </c>
       <c r="D89" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E89" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F89">
         <v>3406</v>
@@ -3583,22 +4031,25 @@
       <c r="G89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B90" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C90">
         <v>2</v>
       </c>
       <c r="D90" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E90" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F90">
         <v>221</v>
@@ -3606,22 +4057,25 @@
       <c r="G90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B91" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C91">
         <v>0</v>
       </c>
       <c r="D91" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E91" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F91">
         <v>1974</v>
@@ -3629,22 +4083,25 @@
       <c r="G91">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H91" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B92" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C92">
         <v>0</v>
       </c>
       <c r="D92" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E92" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F92">
         <v>993</v>
@@ -3652,22 +4109,25 @@
       <c r="G92">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B93" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E93" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F93">
         <v>2521</v>
@@ -3675,22 +4135,25 @@
       <c r="G93">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B94" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C94">
         <v>0</v>
       </c>
       <c r="D94" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E94" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F94">
         <v>2705</v>
@@ -3698,22 +4161,25 @@
       <c r="G94">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B95" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C95">
         <v>0</v>
       </c>
       <c r="D95" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E95" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F95">
         <v>3157</v>
@@ -3721,22 +4187,25 @@
       <c r="G95">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B96" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C96">
         <v>2</v>
       </c>
       <c r="D96" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E96" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F96">
         <v>491</v>
@@ -3744,22 +4213,25 @@
       <c r="G96">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B97" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C97">
         <v>2</v>
       </c>
       <c r="D97" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E97" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F97">
         <v>2210</v>
@@ -3767,22 +4239,25 @@
       <c r="G97">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B98" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C98">
         <v>1</v>
       </c>
       <c r="D98" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E98" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F98">
         <v>2329</v>
@@ -3790,22 +4265,25 @@
       <c r="G98">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H98" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B99" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C99">
         <v>1</v>
       </c>
       <c r="D99" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E99" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F99">
         <v>1666</v>
@@ -3813,22 +4291,25 @@
       <c r="G99">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B100" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C100">
         <v>0</v>
       </c>
       <c r="D100" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E100" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F100">
         <v>1978</v>
@@ -3836,27 +4317,33 @@
       <c r="G100">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H100" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B101" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C101">
         <v>1</v>
       </c>
       <c r="D101" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E101" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F101">
         <v>1461</v>
       </c>
       <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
         <v>0</v>
       </c>
     </row>

--- a/QBAF_relevanceScoreHumanLabeled.xlsx
+++ b/QBAF_relevanceScoreHumanLabeled.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wu-my.sharepoint.com/personal/h12328919_s_wu_ac_at/Documents/Dokumente/Uni/Claude/BA/BA_Code/temp2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="216" documentId="8_{52DC61B2-9161-1B44-B4CB-53D58410C4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C5BF585-6366-6143-B355-E8A4EFCFC581}"/>
+  <xr:revisionPtr revIDLastSave="276" documentId="8_{52DC61B2-9161-1B44-B4CB-53D58410C4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A60D1E9E-3F8F-B845-96F5-A113ED503107}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" xr2:uid="{B9BBEF74-3CC3-0F4D-96E7-5EED1D1E623F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="208">
   <si>
     <t>arg1</t>
   </si>
@@ -1520,15 +1520,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D224C079-FBF6-2442-8650-62051FAE21A1}">
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="66.83203125" customWidth="1"/>
-    <col min="2" max="2" width="86.33203125" customWidth="1"/>
-    <col min="3" max="5" width="1.1640625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="1.33203125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="1.6640625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="62.6640625" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="3" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="10" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2460,7 +2457,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>80</v>
       </c>
@@ -2489,7 +2486,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>82</v>
       </c>
@@ -2518,7 +2515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>84</v>
       </c>
@@ -2547,7 +2544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>85</v>
       </c>
@@ -2576,7 +2573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>87</v>
       </c>
@@ -2605,7 +2602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>89</v>
       </c>
@@ -2634,7 +2631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>91</v>
       </c>
@@ -2663,7 +2660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>93</v>
       </c>
@@ -2692,7 +2689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>95</v>
       </c>
@@ -2721,7 +2718,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>97</v>
       </c>
@@ -2750,7 +2747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>99</v>
       </c>
@@ -2779,7 +2776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>101</v>
       </c>
@@ -2808,7 +2805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>103</v>
       </c>
@@ -2837,7 +2834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>105</v>
       </c>
@@ -2866,7 +2863,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>107</v>
       </c>
@@ -2895,7 +2892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>109</v>
       </c>
@@ -2923,14 +2920,8 @@
       <c r="I48">
         <v>2</v>
       </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>70</v>
       </c>
@@ -2958,14 +2949,8 @@
       <c r="I49">
         <v>1</v>
       </c>
-      <c r="J49">
-        <v>1</v>
-      </c>
-      <c r="K49" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>112</v>
       </c>
@@ -2993,14 +2978,8 @@
       <c r="I50">
         <v>1</v>
       </c>
-      <c r="J50">
-        <v>2</v>
-      </c>
-      <c r="K50" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>114</v>
       </c>
@@ -3029,7 +3008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>116</v>
       </c>
@@ -3058,7 +3037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>118</v>
       </c>
@@ -3087,7 +3066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>120</v>
       </c>
@@ -3116,7 +3095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>122</v>
       </c>
@@ -3145,7 +3124,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>124</v>
       </c>
@@ -3174,7 +3153,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>126</v>
       </c>
@@ -3203,7 +3182,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>128</v>
       </c>
@@ -3228,8 +3207,11 @@
       <c r="H58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>130</v>
       </c>
@@ -3254,8 +3236,11 @@
       <c r="H59">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>132</v>
       </c>
@@ -3280,8 +3265,11 @@
       <c r="H60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>134</v>
       </c>
@@ -3306,8 +3294,11 @@
       <c r="H61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>136</v>
       </c>
@@ -3332,8 +3323,11 @@
       <c r="H62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>138</v>
       </c>
@@ -3358,8 +3352,11 @@
       <c r="H63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>139</v>
       </c>
@@ -3384,8 +3381,11 @@
       <c r="H64">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>140</v>
       </c>
@@ -3410,8 +3410,11 @@
       <c r="H65">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>142</v>
       </c>
@@ -3436,8 +3439,11 @@
       <c r="H66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>144</v>
       </c>
@@ -3462,8 +3468,11 @@
       <c r="H67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>146</v>
       </c>
@@ -3488,8 +3497,11 @@
       <c r="H68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>148</v>
       </c>
@@ -3514,8 +3526,11 @@
       <c r="H69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>150</v>
       </c>
@@ -3540,8 +3555,11 @@
       <c r="H70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>152</v>
       </c>
@@ -3566,8 +3584,11 @@
       <c r="H71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>154</v>
       </c>
@@ -3592,8 +3613,11 @@
       <c r="H72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>156</v>
       </c>
@@ -3618,8 +3642,11 @@
       <c r="H73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>158</v>
       </c>
@@ -3644,8 +3671,11 @@
       <c r="H74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>160</v>
       </c>
@@ -3670,8 +3700,11 @@
       <c r="H75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>39</v>
       </c>
@@ -3696,8 +3729,11 @@
       <c r="H76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>163</v>
       </c>
@@ -3722,8 +3758,11 @@
       <c r="H77">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>165</v>
       </c>
@@ -3748,8 +3787,11 @@
       <c r="H78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>167</v>
       </c>
@@ -3774,8 +3816,11 @@
       <c r="H79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>39</v>
       </c>
@@ -3800,8 +3845,11 @@
       <c r="H80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>170</v>
       </c>
@@ -3826,8 +3874,11 @@
       <c r="H81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>172</v>
       </c>
@@ -3852,8 +3903,11 @@
       <c r="H82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>174</v>
       </c>
@@ -3878,8 +3932,11 @@
       <c r="H83" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>176</v>
       </c>
@@ -3904,8 +3961,11 @@
       <c r="H84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>178</v>
       </c>
@@ -3930,8 +3990,11 @@
       <c r="H85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>180</v>
       </c>
@@ -3956,8 +4019,11 @@
       <c r="H86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>182</v>
       </c>
@@ -3982,8 +4048,11 @@
       <c r="H87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>118</v>
       </c>
@@ -4008,8 +4077,11 @@
       <c r="H88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>185</v>
       </c>
@@ -4034,8 +4106,11 @@
       <c r="H89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>187</v>
       </c>
@@ -4060,8 +4135,11 @@
       <c r="H90" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>189</v>
       </c>
@@ -4086,8 +4164,11 @@
       <c r="H91" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>191</v>
       </c>
@@ -4112,8 +4193,11 @@
       <c r="H92">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>193</v>
       </c>
@@ -4138,8 +4222,11 @@
       <c r="H93">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>195</v>
       </c>
@@ -4164,8 +4251,11 @@
       <c r="H94">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>197</v>
       </c>
@@ -4190,8 +4280,11 @@
       <c r="H95">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>80</v>
       </c>
@@ -4216,8 +4309,11 @@
       <c r="H96">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I96">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>60</v>
       </c>
@@ -4242,8 +4338,11 @@
       <c r="H97">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>201</v>
       </c>
@@ -4268,8 +4367,11 @@
       <c r="H98" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>203</v>
       </c>
@@ -4294,8 +4396,11 @@
       <c r="H99">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>205</v>
       </c>
@@ -4320,8 +4425,11 @@
       <c r="H100" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>206</v>
       </c>
@@ -4345,6 +4453,9 @@
       </c>
       <c r="H101">
         <v>0</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
